--- a/display/excel/campuspulse-demo.xlsx
+++ b/display/excel/campuspulse-demo.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
     <x:sheet name="报名统计" sheetId="2" r:id="Rb4e4fc54f876435e"/>
   </x:sheets>
   <x:calcPr fullCalcOnLoad="1"/>
@@ -166,12 +165,6 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData/>
-</x:worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
